--- a/tests/e2e/fixtures/user_import_invalid_college.xlsx
+++ b/tests/e2e/fixtures/user_import_invalid_college.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,12 +413,15 @@
         <v>college_code</v>
       </c>
       <c r="E1" t="str">
+        <v>program_code</v>
+      </c>
+      <c r="F1" t="str">
         <v>office</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>role</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>password</v>
       </c>
     </row>
@@ -436,12 +439,15 @@
         <v>REQUIRED. Active college code e.g. CCS</v>
       </c>
       <c r="E2" t="str">
+        <v>OPTIONAL. Program code belonging to college e.g. BSIT</v>
+      </c>
+      <c r="F2" t="str">
         <v>OPTIONAL. Office name</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>OPTIONAL. Role (default faculty)</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>OPTIONAL. Blank = password</v>
       </c>
     </row>
@@ -462,15 +468,18 @@
         <v/>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
         <v>faculty</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/e2e/fixtures/user_import_invalid_college.xlsx
+++ b/tests/e2e/fixtures/user_import_invalid_college.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,9 +419,12 @@
         <v>office</v>
       </c>
       <c r="G1" t="str">
+        <v>user_type</v>
+      </c>
+      <c r="H1" t="str">
         <v>role</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>password</v>
       </c>
     </row>
@@ -445,9 +448,12 @@
         <v>OPTIONAL. Office name</v>
       </c>
       <c r="G2" t="str">
+        <v>REQUIRED. faculty|staff|student|external_affiliate</v>
+      </c>
+      <c r="H2" t="str">
         <v>OPTIONAL. Role (default faculty)</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>OPTIONAL. Blank = password</v>
       </c>
     </row>
@@ -474,12 +480,15 @@
         <v>faculty</v>
       </c>
       <c r="H3" t="str">
+        <v>faculty</v>
+      </c>
+      <c r="I3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>